--- a/plot/daily_pic/stats_daily.xlsx
+++ b/plot/daily_pic/stats_daily.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,25 +436,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>risk-free reference point</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>large reference point</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>no risk aversion and risk seeking</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>no loss aversion</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>no probability distortion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
@@ -470,18 +475,21 @@
         <v>0.2936680408743302</v>
       </c>
       <c r="C2" t="n">
+        <v>0.29344047694148</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.3031006955544217</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.3099768503218532</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.5740329626122873</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.2849589023715974</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.4509770900000001</v>
       </c>
     </row>
@@ -495,18 +503,21 @@
         <v>0.4884334156977464</v>
       </c>
       <c r="C3" t="n">
+        <v>0.4682071328387809</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.4636625463763933</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.4752656418310045</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.3729187615957361</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.5788516466426887</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.6699451585250672</v>
       </c>
     </row>
@@ -520,18 +531,21 @@
         <v>0.08867585171338201</v>
       </c>
       <c r="C4" t="n">
+        <v>0.08493740606887577</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.0845212284772691</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.08727323951487517</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.1011352925256691</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.1095818787638278</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.1482809990508</v>
       </c>
     </row>
@@ -545,18 +559,21 @@
         <v>0.1815515664232453</v>
       </c>
       <c r="C5" t="n">
+        <v>0.1814098934245039</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.1822903944642883</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.1836304412383925</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.2711992609138425</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.1893090905059998</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.2213330407182155</v>
       </c>
     </row>
